--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486721_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486721_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2699</v>
+        <v>7.5789</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4213</v>
+        <v>4.5317</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8486</v>
+        <v>3.0472</v>
       </c>
       <c r="G2" t="n">
         <v>3.8894</v>
@@ -610,13 +610,13 @@
         <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1988</v>
+        <v>0.1102</v>
       </c>
       <c r="T2" t="n">
-        <v>0.496</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6948</v>
+        <v>-0.4962</v>
       </c>
       <c r="V2" t="n">
         <v>1.8415</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6463</v>
+        <v>7.0614</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8693</v>
+        <v>4.2347</v>
       </c>
       <c r="F3" t="n">
-        <v>2.777</v>
+        <v>2.8267</v>
       </c>
       <c r="G3" t="n">
         <v>3.5651</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4634</v>
+        <v>-0.0483</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.2824</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3803</v>
+        <v>-0.3307</v>
       </c>
       <c r="V3" t="n">
         <v>1.2277</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3077</v>
+        <v>3.6799</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0374</v>
+        <v>3.736</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7297</v>
+        <v>-0.056</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3848</v>
+        <v>2.9835</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5106</v>
+        <v>0.0559</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1258</v>
+        <v>2.9276</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2827</v>
+        <v>3.4394</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8908</v>
+        <v>0.2631</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6081</v>
+        <v>3.1763</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1021</v>
+        <v>-0.456</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6198</v>
+        <v>-0.2072</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5178</v>
+        <v>-0.2487</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0892</v>
+        <v>-1.1585</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0814</v>
+        <v>-0.2689</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7168</v>
+        <v>0.2273</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3646</v>
+        <v>-0.4962</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1271</v>
+        <v>1.2277</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.741</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9505</v>
+        <v>3.1849</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9568</v>
+        <v>3.9891</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0064</v>
+        <v>-0.8042</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9835</v>
+        <v>4.3848</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0559</v>
+        <v>5.5106</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9276</v>
+        <v>-1.1258</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4394</v>
+        <v>4.2827</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2631</v>
+        <v>4.8908</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1763</v>
+        <v>-0.6081</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.456</v>
+        <v>0.1021</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2072</v>
+        <v>0.6198</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2487</v>
+        <v>-0.5178</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9654</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9984</v>
+        <v>0.9587</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5518</v>
+        <v>0.6685</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4466</v>
+        <v>0.2901</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>2.1271</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.936</v>
+        <v>1.4989</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9491</v>
+        <v>1.4872</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0131</v>
+        <v>0.0117</v>
       </c>
       <c r="G6" t="n">
         <v>1.5573</v>
@@ -922,13 +922,13 @@
         <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9266</v>
+        <v>0.4895</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0479</v>
+        <v>0.5859</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1212</v>
+        <v>-0.0964</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5133</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3541</v>
+        <v>1.43</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2379</v>
+        <v>0.1897</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1161</v>
+        <v>1.2403</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1149</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>0.662</v>
+        <v>0.7379</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7168</v>
+        <v>0.6685</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0548</v>
+        <v>0.0694</v>
       </c>
       <c r="V7" t="n">
         <v>1.2277</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8991</v>
+        <v>0.2149</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0933</v>
+        <v>-2.3301</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1942</v>
+        <v>2.545</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1106</v>
+        <v>-0.3414</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6553</v>
+        <v>-0.6691</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.5447</v>
+        <v>0.3277</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6223</v>
+        <v>-0.6434</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3802</v>
+        <v>-0.8062</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.7579</v>
+        <v>0.1628</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5118</v>
+        <v>0.3021</v>
       </c>
       <c r="N8" t="n">
-        <v>0.275</v>
+        <v>0.1371</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7723</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1168</v>
+        <v>0.7035</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>0.6616</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3867</v>
+        <v>0.0419</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5559</v>
+        <v>2.1698</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3282</v>
+        <v>1.5133</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1901</v>
+        <v>-0.036</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3301</v>
+        <v>-0.359</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5202</v>
+        <v>0.323</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3414</v>
+        <v>-1.0417</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6691</v>
+        <v>2.0621</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3277</v>
+        <v>-3.1039</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6434</v>
+        <v>-1.6198</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8062</v>
+        <v>1.0975</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1628</v>
+        <v>-2.7172</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3021</v>
+        <v>0.578</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1371</v>
+        <v>0.9646</v>
       </c>
       <c r="O9" t="n">
-        <v>0.165</v>
+        <v>-0.3866</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3169</v>
+        <v>0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6786</v>
+        <v>0.8552</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6616</v>
+        <v>0.4272</v>
       </c>
       <c r="U9" t="n">
-        <v>0.017</v>
+        <v>0.428</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1698</v>
+        <v>-0.0426</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5133</v>
+        <v>1.7989</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6565</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2151</v>
+        <v>-0.0827</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.855</v>
+        <v>-0.6482</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6399</v>
+        <v>0.5654</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2758</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0607</v>
+        <v>0.193</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1655</v>
+        <v>0.0413</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2262</v>
+        <v>0.1518</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1061</v>
+        <v>-0.6385</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5036</v>
+        <v>-0.196</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3975</v>
+        <v>-0.4426</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0417</v>
+        <v>0.1106</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0621</v>
+        <v>3.6553</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1039</v>
+        <v>-3.5447</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6198</v>
+        <v>0.6223</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0975</v>
+        <v>3.3802</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7172</v>
+        <v>-2.7579</v>
       </c>
       <c r="M11" t="n">
-        <v>0.578</v>
+        <v>-0.5118</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9646</v>
+        <v>0.275</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3866</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2149</v>
+        <v>1.5792</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7174</v>
+        <v>1.4407</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.1384</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0426</v>
+        <v>-1.5559</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7989</v>
+        <v>-0.3282</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8415</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8235</v>
+        <v>-1.931</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0271</v>
+        <v>-1.234</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7964</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1984</v>
@@ -1390,13 +1390,13 @@
         <v>0.7723</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4521</v>
+        <v>0.3446</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9375</v>
+        <v>0.7307</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4854</v>
+        <v>-0.386</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8842</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.409</v>
+        <v>21.9607</v>
       </c>
       <c r="E13" t="n">
-        <v>12.8493</v>
+        <v>13.4011</v>
       </c>
       <c r="F13" t="n">
-        <v>8.559500000000002</v>
+        <v>8.5594</v>
       </c>
       <c r="G13" t="n">
         <v>13.5185</v>
@@ -1468,13 +1468,13 @@
         <v>16.4117</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1027</v>
+        <v>5.6546</v>
       </c>
       <c r="T13" t="n">
-        <v>5.7888</v>
+        <v>6.3405</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6861000000000002</v>
+        <v>-0.6859</v>
       </c>
       <c r="V13" t="n">
         <v>0.8568999999999993</v>
@@ -1483,7 +1483,7 @@
         <v>9.322699999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.4659</v>
+        <v>-8.465900000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9557</v>
+        <v>1.9919</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4481</v>
+        <v>4.3105</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4924</v>
+        <v>-2.3186</v>
       </c>
       <c r="G14" t="n">
         <v>1.4503</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7498</v>
+        <v>-0.214</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5991</v>
+        <v>0.4615</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.6754</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9822</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6392</v>
+        <v>1.0847</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2017</v>
+        <v>3.9948</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5625</v>
+        <v>-2.9101</v>
       </c>
       <c r="G15" t="n">
         <v>1.4922</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8166</v>
+        <v>0.2621</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7168</v>
+        <v>0.5099</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0998</v>
+        <v>-0.2478</v>
       </c>
       <c r="V15" t="n">
         <v>3.192</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1093</v>
+        <v>-0.8002</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9914</v>
+        <v>-0.1104</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8821</v>
+        <v>-0.6898</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1981</v>
+        <v>0.6895</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7446</v>
+        <v>0.2758</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9427</v>
+        <v>0.4137</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5406</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2278</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6872</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7387</v>
+        <v>0.6895</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4832</v>
+        <v>0.2758</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2555</v>
+        <v>0.4137</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3129</v>
+        <v>-0.262</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7925</v>
+        <v>-0.1104</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4797</v>
+        <v>-0.1516</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0401</v>
+        <v>-1.2277</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8168</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8568</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8747</v>
+        <v>-1.0934</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1104</v>
+        <v>-2.1823</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7643</v>
+        <v>1.0889</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6895</v>
+        <v>-0.63</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2758</v>
+        <v>-2.9381</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4137</v>
+        <v>2.3081</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-1.6271</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.6534</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6895</v>
+        <v>0.3437</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2758</v>
+        <v>-1.311</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4137</v>
+        <v>1.6548</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.3515</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3365</v>
+        <v>-1.1585</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1104</v>
+        <v>-0.359</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2261</v>
+        <v>-0.7995</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9941</v>
+        <v>-1.2311</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1823</v>
+        <v>0.7504</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1882</v>
+        <v>-1.9814</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.63</v>
+        <v>-0.1981</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.9381</v>
+        <v>0.7446</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3081</v>
+        <v>-0.9427</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9737</v>
+        <v>0.5406</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6271</v>
+        <v>1.2278</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6534</v>
+        <v>-0.6872</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3437</v>
+        <v>-0.7387</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.311</v>
+        <v>-0.4832</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6548</v>
+        <v>-0.2555</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3515</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0591</v>
+        <v>-0.0275</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.359</v>
+        <v>0.5515</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7002</v>
+        <v>-0.579</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6565</v>
+        <v>-0.0401</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6565</v>
+        <v>0.8168</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3499</v>
+        <v>-1.3748</v>
       </c>
       <c r="E19" t="n">
         <v>1.0144</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3643</v>
+        <v>-2.3891</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0487</v>
@@ -1936,13 +1936,13 @@
         <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0167</v>
+        <v>-0.0415</v>
       </c>
       <c r="T19" t="n">
         <v>0.2201</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2368</v>
+        <v>-0.2616</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4084</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>G. COMACHIO COACHMAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0243</v>
+        <v>-1.6656</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9247</v>
+        <v>-0.2455</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0996</v>
+        <v>-1.4201</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5043</v>
+        <v>-1.0713</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0002</v>
+        <v>-0.6282</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5041</v>
+        <v>-0.4431</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6488</v>
+        <v>0.1436</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.0622</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6488</v>
+        <v>0.0814</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1445</v>
+        <v>-1.2149</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0002</v>
+        <v>-0.6904</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1447</v>
+        <v>-0.5245</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2923</v>
+        <v>-1.1032</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2759</v>
+        <v>-0.2485</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0164</v>
+        <v>-0.8547</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2277</v>
+        <v>0.1228</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2455</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. HERNÁNDEZ TRUJILLO</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2557</v>
+        <v>-2.0491</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8414</v>
+        <v>-0.9247</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5856</v>
+        <v>-1.1245</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.518</v>
+        <v>-0.5043</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2</v>
+        <v>-0.0002</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.318</v>
+        <v>-0.5041</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3999</v>
+        <v>-0.6488</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0616</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3383</v>
+        <v>-0.6488</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1181</v>
+        <v>0.1445</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1384</v>
+        <v>-0.0002</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0203</v>
+        <v>0.1447</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1086</v>
+        <v>-0.3172</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4415</v>
+        <v>-0.2759</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6672</v>
+        <v>-0.0413</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9847</v>
+        <v>-1.2277</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9847</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. COMACHIO COACHMAN</t>
+          <t>J. HERNÁNDEZ TRUJILLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3276</v>
+        <v>-2.0986</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6592</v>
+        <v>-2.6345</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6684</v>
+        <v>0.536</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0713</v>
+        <v>-2.518</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6282</v>
+        <v>-1.2</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4431</v>
+        <v>-1.318</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1436</v>
+        <v>-2.3999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0622</v>
+        <v>-1.0616</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0814</v>
+        <v>-1.3383</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2149</v>
+        <v>-0.1181</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6904</v>
+        <v>-0.1384</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5245</v>
+        <v>0.0203</v>
       </c>
       <c r="P22" t="n">
         <v>0.3862</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7652</v>
+        <v>-0.9514</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6622</v>
+        <v>-0.2346</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.103</v>
+        <v>-0.7168</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1228</v>
+        <v>0.9847</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2455</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1228</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.431</v>
+        <v>-3.6077</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.677</v>
+        <v>-2.9531</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.754</v>
+        <v>-0.6546</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2642</v>
@@ -2248,13 +2248,13 @@
         <v>1.3515</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0094</v>
+        <v>-0.1861</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4415</v>
+        <v>0.2825</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.4686</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1228</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7797</v>
+        <v>-5.2047</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.736</v>
+        <v>-4.0121</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0437</v>
+        <v>-1.1927</v>
       </c>
       <c r="G24" t="n">
         <v>-1.481</v>
@@ -2326,13 +2326,13 @@
         <v>1.9308</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3956</v>
+        <v>-0.8206</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9381</v>
+        <v>-0.2141</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4575</v>
+        <v>-0.6065</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7792</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.076</v>
+        <v>-5.3602</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.0842</v>
+        <v>-5.5671</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0083</v>
+        <v>0.2069</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4347</v>
@@ -2404,13 +2404,13 @@
         <v>2.1239</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9986</v>
+        <v>-0.2829</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4142</v>
+        <v>0.1029</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5845</v>
+        <v>-0.3858</v>
       </c>
       <c r="V25" t="n">
         <v>0.2882</v>
@@ -2440,10 +2440,10 @@
         <v>-21.4088</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.559600000000001</v>
+        <v>-8.5596</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.8492</v>
+        <v>-12.8491</v>
       </c>
       <c r="G26" t="n">
         <v>-13.5183</v>
@@ -2452,10 +2452,10 @@
         <v>-15.5192</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0008</v>
+        <v>2.000800000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.299899999999999</v>
+        <v>-1.2999</v>
       </c>
       <c r="K26" t="n">
         <v>-2.4081</v>
@@ -2482,19 +2482,19 @@
         <v>14.4809</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.1027</v>
+        <v>-5.102799999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6857000000000003</v>
+        <v>0.6859</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.7889</v>
+        <v>-5.788600000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.8568999999999998</v>
+        <v>-0.8568999999999993</v>
       </c>
       <c r="W26" t="n">
-        <v>8.4659</v>
+        <v>8.465899999999998</v>
       </c>
       <c r="X26" t="n">
         <v>-9.322899999999999</v>
